--- a/output/pdf_financials_xlsx/ZCC.H.xlsx
+++ b/output/pdf_financials_xlsx/ZCC.H.xlsx
@@ -1063,55 +1063,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.041829</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.03596</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.022369</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02885</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.029751</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.028526</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.025189</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.017879</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.015055</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.017487</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.024979</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.028913</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.018073</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00657</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.019218</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.053874</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.059071</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -2086,55 +2086,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.088397</v>
+        <v>-0.130226</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.812689</v>
+        <v>-0.848649</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.291213</v>
+        <v>-0.313582</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.121907</v>
+        <v>-0.150757</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.099049</v>
+        <v>-0.1288</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.23446</v>
+        <v>-0.262986</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.06962400000000001</v>
+        <v>-0.09481299999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.056682</v>
+        <v>-0.074561</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.069245</v>
+        <v>-0.0843</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.068702</v>
+        <v>-0.086189</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.68088</v>
+        <v>-0.705859</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.205862</v>
+        <v>-0.234775</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.095939</v>
+        <v>0.077866</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.07098</v>
+        <v>-0.07754999999999999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.080289</v>
+        <v>-0.099507</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.047977</v>
+        <v>-0.101851</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.038928</v>
+        <v>-0.097999</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>-0.152849</v>
@@ -2208,55 +2208,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.088397</v>
+        <v>-0.130226</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.812689</v>
+        <v>-0.848649</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.291213</v>
+        <v>-0.313582</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.121907</v>
+        <v>-0.150757</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.099049</v>
+        <v>-0.1288</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.23446</v>
+        <v>-0.262986</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.06962400000000001</v>
+        <v>-0.09481299999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.056682</v>
+        <v>-0.074561</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.069245</v>
+        <v>-0.0843</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.068702</v>
+        <v>-0.086189</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.68088</v>
+        <v>-0.705859</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.205862</v>
+        <v>-0.234775</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.095939</v>
+        <v>0.077866</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.07098</v>
+        <v>-0.07754999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.080289</v>
+        <v>-0.099507</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.047977</v>
+        <v>-0.101851</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.038928</v>
+        <v>-0.097999</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>-0.152849</v>
@@ -30186,7 +30186,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZCC.H.xlsx
+++ b/output/pdf_financials_xlsx/ZCC.H.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.027421</v>
+        <v>0.051766</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.027793</v>
@@ -767,49 +767,49 @@
         <v>0.022236</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.019736</v>
+        <v>0.049736</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.024626</v>
+        <v>0.054626</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.033738</v>
+        <v>0.063738</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.023453</v>
+        <v>0.053453</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.01841</v>
+        <v>0.04841</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.026552</v>
+        <v>0.056552</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.026909</v>
+        <v>0.056909</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.020052</v>
+        <v>0.056052</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.026734</v>
+        <v>0.062734</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.023512</v>
+        <v>0.059512</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.018454</v>
+        <v>0.054454</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.020792</v>
+        <v>0.056792</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.024899</v>
+        <v>0.060899</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.027176</v>
+        <v>0.063176</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.030641</v>
+        <v>0.06664100000000001</v>
       </c>
     </row>
     <row r="8">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.035998</v>
+        <v>0.060343</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.033225</v>
@@ -950,49 +950,49 @@
         <v>0.02614</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.02397</v>
+        <v>0.05397</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.028419</v>
+        <v>0.058419</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.037783</v>
+        <v>0.067783</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.027775</v>
+        <v>0.057775</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.02285</v>
+        <v>0.05285</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.030698</v>
+        <v>0.060698</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.031149</v>
+        <v>0.061149</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.023931</v>
+        <v>0.059931</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.030425</v>
+        <v>0.066425</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.027826</v>
+        <v>0.06382599999999999</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.022481</v>
+        <v>0.058481</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.025111</v>
+        <v>0.061111</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.030901</v>
+        <v>0.066901</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.033374</v>
+        <v>0.06937400000000001</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.037737</v>
+        <v>0.073737</v>
       </c>
     </row>
     <row r="11">
@@ -1114,7 +1114,7 @@
         <v>0.059071</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.035878</v>
       </c>
     </row>
     <row r="13">
@@ -2137,7 +2137,7 @@
         <v>-0.097999</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.152849</v>
+        <v>-0.188727</v>
       </c>
     </row>
     <row r="28">
@@ -2259,7 +2259,7 @@
         <v>-0.097999</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.152849</v>
+        <v>-0.188727</v>
       </c>
     </row>
     <row r="30">
@@ -2765,7 +2765,7 @@
         <v>0.059741</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0</v>
+        <v>0.040327</v>
       </c>
     </row>
     <row r="38">
@@ -3009,7 +3009,7 @@
         <v>0.059741</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>0</v>
+        <v>0.040327</v>
       </c>
     </row>
     <row r="42">
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.04919</v>
+        <v>0.008862999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4709,22 +4709,22 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.10782</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.14503</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.163647</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.192074</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.210602</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.2098</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.207692</v>
@@ -4733,16 +4733,16 @@
         <v>0.211513</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.218222</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.231496</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.25266</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.265443</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>0.01643</v>
@@ -5136,22 +5136,22 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.30782</v>
+        <v>0.2</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.29003</v>
+        <v>0.145</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.308647</v>
+        <v>0.145</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.328574</v>
+        <v>0.1365</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.330602</v>
+        <v>0.12</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.3168</v>
+        <v>0.107</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.094</v>
@@ -5160,16 +5160,16 @@
         <v>0.079</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.297222</v>
+        <v>0.079</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.310496</v>
+        <v>0.079</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.33166</v>
+        <v>0.079</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.344443</v>
+        <v>0.079</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0</v>
@@ -6041,58 +6041,58 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>3.696572</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>3.752822</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>3.788422</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>3.825922</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>3.825922</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>3.825922</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>3.825922</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>3.825922</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>0</v>
+        <v>4.220306</v>
       </c>
     </row>
     <row r="89">
@@ -6324,25 +6324,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.747013</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.723885</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.955113</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.303213</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.458402</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.458402</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.458402</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>1.458402</v>
@@ -9270,7 +9270,11 @@
           <t>Amounts receivable – Note 5</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -9760,7 +9764,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10172,7 +10180,11 @@
           <t>Share capital – Note 6 and 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10276,7 +10288,11 @@
           <t>Share capital – Notes 6 and 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10480,7 +10496,11 @@
           <t>Share capital – Notes 6, 7 and 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10682,7 +10702,11 @@
           <t>Accounts payable and accrued liabilities – Notes 8 and 9 $</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10870,7 +10894,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -11376,7 +11404,11 @@
           <t>Accounts payable and accrued liabilities – Notes 6 and 9 $</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11476,7 +11508,11 @@
           <t>Share capital – Notes 5, 6 and 7</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12524,7 +12560,11 @@
           <t>Share capital – Note 7 3,788,422</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12628,7 +12668,11 @@
           <t>Contributed surplus – Note 7 955,113</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12938,7 +12982,11 @@
           <t>Accounts payable and accrued liabilities – Notes 3, 5 and 7 $</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.10782</v>
       </c>
@@ -13142,7 +13190,11 @@
           <t>Share capital – Note 4</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>3.696572</v>
       </c>
@@ -13244,7 +13296,11 @@
           <t>Contributed surplus – Note 4</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -29112,7 +29168,11 @@
           <t>Management fees – Note 8</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -29732,7 +29792,11 @@
           <t>Interest income – Note 5</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -32284,7 +32348,11 @@
           <t>Consulting fees – Note 5</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E232" s="5" t="n">
         <v>0.020595</v>
       </c>
@@ -32604,7 +32672,11 @@
           <t>Rent – Note 5</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E235" s="5" t="n">
         <v>0.00375</v>
       </c>

--- a/output/pdf_financials_xlsx/ZCC.H.xlsx
+++ b/output/pdf_financials_xlsx/ZCC.H.xlsx
@@ -26850,7 +26850,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
